--- a/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 15,08</t>
+          <t>3,32; 15,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 13,73</t>
+          <t>2,0; 14,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 13,42</t>
+          <t>-4,75; 13,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 11,24</t>
+          <t>-2,67; 11,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 3,62</t>
+          <t>-9,06; 3,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,63; -2,48</t>
+          <t>-19,24; -2,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,2</t>
+          <t>2,41; 11,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 7,45</t>
+          <t>-1,51; 7,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 3,02</t>
+          <t>-9,28; 3,9</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,23; 70,59</t>
+          <t>12,36; 71,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 62,65</t>
+          <t>7,58; 66,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 59,19</t>
+          <t>-18,48; 59,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 29,92</t>
+          <t>-6,16; 30,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,02; 9,99</t>
+          <t>-22,25; 9,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,91; -6,89</t>
+          <t>-46,69; -6,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 37,42</t>
+          <t>7,52; 38,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 24,98</t>
+          <t>-4,79; 23,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 9,98</t>
+          <t>-28,41; 12,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 14,59</t>
+          <t>4,44; 14,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 4,39</t>
+          <t>-5,93; 4,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 4,73</t>
+          <t>-9,11; 4,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 10,38</t>
+          <t>-1,35; 10,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 2,44</t>
+          <t>-8,87; 2,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,07; -13,79</t>
+          <t>-31,09; -13,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,07</t>
+          <t>3,59; 11,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 2,78</t>
+          <t>-5,62; 2,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,63; -6,18</t>
+          <t>-17,36; -6,1</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 51,22</t>
+          <t>13,79; 52,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 15,26</t>
+          <t>-17,96; 15,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 15,71</t>
+          <t>-27,51; 15,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 24,69</t>
+          <t>-2,8; 25,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 5,5</t>
+          <t>-18,41; 6,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,49; -32,67</t>
+          <t>-66,36; -32,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 30,85</t>
+          <t>9,15; 32,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 7,76</t>
+          <t>-14,52; 6,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,76; -17,62</t>
+          <t>-45,69; -17,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 11,98</t>
+          <t>0,42; 11,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,93</t>
+          <t>-5,84; 5,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,23; -6,19</t>
+          <t>-17,22; -6,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 8,11</t>
+          <t>-3,24; 7,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -0,04</t>
+          <t>-11,16; -0,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,46; -20,78</t>
+          <t>-34,3; -20,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 7,82</t>
+          <t>-0,05; 7,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 0,18</t>
+          <t>-7,41; 0,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,11; -15,57</t>
+          <t>-24,17; -15,67</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 34,84</t>
+          <t>1,07; 34,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 14,44</t>
+          <t>-14,66; 14,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,51; -17,85</t>
+          <t>-43,82; -18,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 15,4</t>
+          <t>-5,59; 14,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,56; -0,21</t>
+          <t>-18,89; -1,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,55; -39,3</t>
+          <t>-61,24; -38,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 17,5</t>
+          <t>-0,14; 17,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 0,41</t>
+          <t>-14,85; 0,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,93; -34,84</t>
+          <t>-50,39; -35,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 7,28</t>
+          <t>-5,27; 6,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 10,32</t>
+          <t>-2,27; 10,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-38,71; -9,46</t>
+          <t>-41,3; -10,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 12,39</t>
+          <t>0,85; 12,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 0,71</t>
+          <t>-10,38; 1,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-32,28; -19,36</t>
+          <t>-31,57; -19,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 8,21</t>
+          <t>-0,69; 8,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,72</t>
+          <t>-4,88; 3,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-39,22; -16,95</t>
+          <t>-39,7; -17,0</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 15,09</t>
+          <t>-9,6; 14,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 22,05</t>
+          <t>-4,06; 21,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,7; -18,95</t>
+          <t>-76,56; -20,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 19,5</t>
+          <t>1,2; 19,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 1,3</t>
+          <t>-15,01; 2,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,3; -30,58</t>
+          <t>-47,53; -30,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 14,76</t>
+          <t>-1,37; 14,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 6,61</t>
+          <t>-7,98; 6,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-66,85; -29,48</t>
+          <t>-64,45; -29,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 6,76</t>
+          <t>-4,88; 6,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,27; -3,74</t>
+          <t>-16,55; -3,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -18,32</t>
+          <t>-30,28; -18,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,61; 12,67</t>
+          <t>2,39; 12,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 8,09</t>
+          <t>-2,72; 7,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,72; -19,89</t>
+          <t>-30,54; -20,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 8,47</t>
+          <t>0,46; 8,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 0,35</t>
+          <t>-7,54; 1,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-28,78; -21,04</t>
+          <t>-28,44; -20,49</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 9,3</t>
+          <t>-6,15; 9,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,24; -4,97</t>
+          <t>-20,69; -4,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,35; -24,59</t>
+          <t>-37,77; -24,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3,12; 16,64</t>
+          <t>2,88; 16,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 10,46</t>
+          <t>-3,33; 10,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,19; -26,13</t>
+          <t>-36,77; -26,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,39; 11,15</t>
+          <t>0,61; 10,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 0,45</t>
+          <t>-9,31; 1,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,88; -27,56</t>
+          <t>-35,31; -26,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>8,07; 18,83</t>
+          <t>7,94; 18,29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,39; 13,84</t>
+          <t>2,6; 13,91</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-32,61; -20,75</t>
+          <t>-32,62; -20,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 5,19</t>
+          <t>-2,47; 5,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 2,06</t>
+          <t>-5,66; 2,48</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-29,23; -1,46</t>
+          <t>-28,95; -2,65</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,05</t>
+          <t>3,94; 10,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 6,33</t>
+          <t>-0,75; 5,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -3,78</t>
+          <t>-28,34; -3,68</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9,77; 24,87</t>
+          <t>9,7; 24,07</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2,87; 18,1</t>
+          <t>3,16; 18,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-39,04; -26,55</t>
+          <t>-38,74; -26,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,73</t>
+          <t>-2,62; 5,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 2,2</t>
+          <t>-5,99; 2,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-31,11; -1,61</t>
+          <t>-30,99; -2,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,82</t>
+          <t>4,44; 12,04</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,42</t>
+          <t>-0,84; 6,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-32,18; -4,33</t>
+          <t>-32,4; -4,52</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,13</t>
+          <t>-1,65; 7,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 5,64</t>
+          <t>-3,51; 5,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-26,33; -15,51</t>
+          <t>-26,26; -15,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 4,7</t>
+          <t>-1,15; 4,72</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,02</t>
+          <t>-1,86; 3,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-23,16; -15,29</t>
+          <t>-23,26; -15,61</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,33</t>
+          <t>-0,54; 4,29</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,28</t>
+          <t>-1,48; 3,45</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-23,22; -16,91</t>
+          <t>-22,83; -16,91</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 7,98</t>
+          <t>-1,73; 7,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 6,34</t>
+          <t>-3,7; 5,8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,73; -17,16</t>
+          <t>-27,75; -17,18</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 5,03</t>
+          <t>-1,16; 5,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 4,34</t>
+          <t>-1,92; 4,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-23,88; -16,33</t>
+          <t>-24,07; -16,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,66</t>
+          <t>-0,53; 4,62</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,54</t>
+          <t>-1,54; 3,71</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-24,32; -18,04</t>
+          <t>-23,99; -18,24</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5,26; 10,26</t>
+          <t>4,98; 9,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,72</t>
+          <t>1,53; 6,45</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-17,65; -5,95</t>
+          <t>-19,03; -6,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,79</t>
+          <t>3,28; 7,81</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,12</t>
+          <t>-2,29; 2,26</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -6,66</t>
+          <t>-20,14; -5,94</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,23</t>
+          <t>4,75; 8,25</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,71</t>
+          <t>0,3; 3,68</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -7,64</t>
+          <t>-16,89; -8,09</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>10,68; 21,92</t>
+          <t>10,07; 20,69</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,7</t>
+          <t>3,1; 13,71</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,69; -12,61</t>
+          <t>-39,72; -13,03</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5,0; 12,48</t>
+          <t>5,04; 12,39</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 3,37</t>
+          <t>-3,54; 3,61</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-31,03; -10,23</t>
+          <t>-31,28; -9,37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,45; 14,83</t>
+          <t>8,27; 14,88</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,73</t>
+          <t>0,54; 6,71</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-29,91; -13,73</t>
+          <t>-30,06; -14,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>-0,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-11,34</t>
+          <t>-11,22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,38</t>
+          <t>-5,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 15,25</t>
+          <t>3,07; 14,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 14,14</t>
+          <t>1,18; 13,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 13,36</t>
+          <t>-8,07; 7,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 11,12</t>
+          <t>-1,88; 10,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 3,46</t>
+          <t>-8,71; 3,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,24; -2,72</t>
+          <t>-18,25; -3,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 11,34</t>
+          <t>2,52; 11,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 7,17</t>
+          <t>-1,93; 7,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 3,9</t>
+          <t>-11,05; 0,02</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>-3,5%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-28,76%</t>
+          <t>-28,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,62%</t>
+          <t>-18,76%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,36; 71,43</t>
+          <t>11,7; 63,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 66,36</t>
+          <t>4,43; 62,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 59,43</t>
+          <t>-30,84; 31,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 30,77</t>
+          <t>-4,69; 28,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 9,25</t>
+          <t>-20,41; 9,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,69; -6,57</t>
+          <t>-45,03; -9,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 38,61</t>
+          <t>7,12; 39,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 23,97</t>
+          <t>-5,88; 24,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 12,96</t>
+          <t>-33,28; 0,16</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-3,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-20,69</t>
+          <t>-18,45</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-11,11</t>
+          <t>-10,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 14,79</t>
+          <t>4,46; 14,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 4,42</t>
+          <t>-6,09; 4,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 4,7</t>
+          <t>-10,26; 2,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 10,66</t>
+          <t>-1,39; 9,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 2,78</t>
+          <t>-8,94; 2,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,09; -13,4</t>
+          <t>-24,35; -12,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 11,27</t>
+          <t>3,67; 10,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 2,23</t>
+          <t>-4,98; 2,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -6,1</t>
+          <t>-14,97; -6,29</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,31%</t>
+          <t>-12,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-46,02%</t>
+          <t>-41,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-29,75%</t>
+          <t>-28,45%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,79; 52,27</t>
+          <t>13,69; 52,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 15,29</t>
+          <t>-18,39; 15,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 15,43</t>
+          <t>-30,66; 9,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 25,62</t>
+          <t>-2,94; 24,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 6,34</t>
+          <t>-17,92; 5,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,36; -32,21</t>
+          <t>-51,57; -29,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 32,3</t>
+          <t>9,69; 30,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 6,44</t>
+          <t>-12,82; 8,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,69; -17,04</t>
+          <t>-38,12; -17,38</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-11,93</t>
+          <t>-12,63</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-26,48</t>
+          <t>-24,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-19,46</t>
+          <t>-18,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 11,77</t>
+          <t>0,71; 11,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 5,07</t>
+          <t>-5,96; 5,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,22; -6,21</t>
+          <t>-18,51; -7,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 7,48</t>
+          <t>-3,17; 7,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,16; -0,65</t>
+          <t>-10,77; -0,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,3; -20,72</t>
+          <t>-29,13; -19,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 7,99</t>
+          <t>0,11; 7,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 0,29</t>
+          <t>-7,5; 0,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,17; -15,67</t>
+          <t>-21,92; -14,66</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-32,37%</t>
+          <t>-34,27%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-47,4%</t>
+          <t>-43,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-41,65%</t>
+          <t>-40,21%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 34,92</t>
+          <t>1,86; 33,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 14,91</t>
+          <t>-15,27; 14,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,82; -18,25</t>
+          <t>-46,69; -22,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 14,24</t>
+          <t>-5,41; 13,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,89; -1,22</t>
+          <t>-18,46; -1,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,24; -38,63</t>
+          <t>-49,69; -36,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 17,96</t>
+          <t>0,23; 17,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 0,79</t>
+          <t>-15,38; 1,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,39; -35,0</t>
+          <t>-45,46; -32,71</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-22,92</t>
+          <t>-12,66</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-24,98</t>
+          <t>-23,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-24,67</t>
+          <t>-17,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 6,91</t>
+          <t>-4,64; 7,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 10,09</t>
+          <t>-1,57; 10,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-41,3; -10,01</t>
+          <t>-18,39; -6,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 12,22</t>
+          <t>1,06; 12,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 1,28</t>
+          <t>-10,56; 1,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,57; -19,62</t>
+          <t>-28,55; -18,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 8,02</t>
+          <t>-0,13; 8,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 3,75</t>
+          <t>-4,3; 4,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-39,7; -17,0</t>
+          <t>-21,53; -14,09</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-44,99%</t>
+          <t>-24,85%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-37,49%</t>
+          <t>-35,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-41,98%</t>
+          <t>-30,57%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 14,55</t>
+          <t>-8,67; 15,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 21,46</t>
+          <t>-2,84; 21,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-76,56; -20,46</t>
+          <t>-33,96; -13,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 19,23</t>
+          <t>1,54; 19,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 2,01</t>
+          <t>-15,05; 2,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,53; -30,96</t>
+          <t>-40,86; -28,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 14,06</t>
+          <t>-0,19; 14,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 6,7</t>
+          <t>-7,01; 7,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-64,45; -29,11</t>
+          <t>-35,59; -24,96</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-24,03</t>
+          <t>-25,43</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,22 +1513,22 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>-24,94</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,26</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-3,48</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>-25,22</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,26</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-3,48</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-24,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 6,72</t>
+          <t>-5,63; 6,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,55; -3,38</t>
+          <t>-15,48; -3,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-30,28; -18,39</t>
+          <t>-31,05; -19,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 12,66</t>
+          <t>2,52; 12,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 7,75</t>
+          <t>-2,31; 8,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,54; -20,45</t>
+          <t>-30,07; -20,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 8,18</t>
+          <t>0,39; 7,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 1,36</t>
+          <t>-7,67; 0,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -20,49</t>
+          <t>-28,98; -21,38</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-31,27%</t>
+          <t>-33,08%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,46%</t>
+          <t>-31,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-31,42%</t>
+          <t>-32,1%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 9,19</t>
+          <t>-7,1; 8,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -4,42</t>
+          <t>-19,88; -4,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,77; -24,61</t>
+          <t>-39,3; -26,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2,88; 16,52</t>
+          <t>3,08; 16,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 10,05</t>
+          <t>-2,75; 10,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,77; -26,45</t>
+          <t>-36,12; -25,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,61; 10,84</t>
+          <t>0,34; 10,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 1,74</t>
+          <t>-9,53; 0,53</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,31; -26,67</t>
+          <t>-36,08; -27,99</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-26,56</t>
+          <t>-27,23</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-15,78</t>
+          <t>-27,15</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-18,84</t>
+          <t>-27,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>7,94; 18,29</t>
+          <t>7,98; 18,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,6; 13,91</t>
+          <t>2,8; 13,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-32,62; -20,6</t>
+          <t>-32,81; -20,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 5,04</t>
+          <t>-1,79; 5,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 2,48</t>
+          <t>-5,56; 2,34</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-28,95; -2,65</t>
+          <t>-31,11; -22,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,94; 10,2</t>
+          <t>3,67; 10,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,79</t>
+          <t>-0,69; 6,41</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-28,34; -3,68</t>
+          <t>-31,02; -23,64</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-32,83%</t>
+          <t>-33,67%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-16,99%</t>
+          <t>-29,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-21,57%</t>
+          <t>-31,4%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9,7; 24,07</t>
+          <t>9,66; 23,98</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,16; 18,02</t>
+          <t>3,33; 17,22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-38,74; -26,42</t>
+          <t>-39,43; -26,66</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 5,54</t>
+          <t>-1,88; 5,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 2,77</t>
+          <t>-5,9; 2,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-30,99; -2,89</t>
+          <t>-33,1; -25,13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,44; 12,04</t>
+          <t>4,08; 11,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 6,81</t>
+          <t>-0,76; 7,48</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -4,52</t>
+          <t>-34,76; -27,37</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-20,94</t>
+          <t>-21,37</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-19,43</t>
+          <t>-19,86</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-20,07</t>
+          <t>-20,51</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 7,1</t>
+          <t>-1,93; 7,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 5,21</t>
+          <t>-3,32; 5,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-26,26; -15,53</t>
+          <t>-26,94; -15,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,72</t>
+          <t>-0,95; 4,98</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,92</t>
+          <t>-2,13; 4,27</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-23,26; -15,61</t>
+          <t>-23,28; -15,8</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,29</t>
+          <t>-0,5; 4,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,45</t>
+          <t>-1,67; 3,45</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-22,83; -16,91</t>
+          <t>-23,27; -17,15</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-22,52%</t>
+          <t>-22,98%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-20,28%</t>
+          <t>-20,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-21,19%</t>
+          <t>-21,65%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 7,95</t>
+          <t>-2,02; 7,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 5,8</t>
+          <t>-3,47; 5,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,75; -17,18</t>
+          <t>-28,46; -16,72</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 5,05</t>
+          <t>-0,98; 5,33</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,18</t>
+          <t>-2,16; 4,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-24,07; -16,74</t>
+          <t>-23,98; -16,82</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,62</t>
+          <t>-0,52; 4,68</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,71</t>
+          <t>-1,73; 3,7</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-23,99; -18,24</t>
+          <t>-24,35; -18,39</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-10,03</t>
+          <t>-8,58</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-15,92</t>
+          <t>-17,57</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-12,92</t>
+          <t>-13,1</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,73</t>
+          <t>5,07; 9,89</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,45</t>
+          <t>1,38; 6,46</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-19,03; -6,18</t>
+          <t>-11,21; -6,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,81</t>
+          <t>3,14; 7,82</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,26</t>
+          <t>-2,34; 2,34</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-20,14; -5,94</t>
+          <t>-19,68; -15,47</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,25</t>
+          <t>4,62; 8,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,68</t>
+          <t>0,32; 3,68</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-16,89; -8,09</t>
+          <t>-14,76; -11,23</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-20,84%</t>
+          <t>-17,82%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-24,93%</t>
+          <t>-27,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-23,03%</t>
+          <t>-23,35%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>10,07; 20,69</t>
+          <t>10,08; 21,02</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3,1; 13,71</t>
+          <t>2,89; 13,8</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-39,72; -13,03</t>
+          <t>-22,63; -13,1</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,39</t>
+          <t>4,75; 12,4</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,61</t>
+          <t>-3,62; 3,72</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-31,28; -9,37</t>
+          <t>-30,25; -24,72</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,27; 14,88</t>
+          <t>8,08; 14,57</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,71</t>
+          <t>0,62; 6,67</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-30,06; -14,5</t>
+          <t>-25,85; -20,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
